--- a/outputs/screener/epc_earnings_quality_screener.xlsx
+++ b/outputs/screener/epc_earnings_quality_screener.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>KEC_AR_FY26.pdf p.117 (balance sheet) p.118 (P&amp;L and cash flow)</t>
+          <t>KEC_AR_FY26.pdf p.117 (balance sheet) p.118 (P&amp;L "PROFIT FOR THE YEAR AFTER TAX" 605.59 and cash flow). Consolidated equity shows no non-controlling interest, so this is total group profit.</t>
         </is>
       </c>
     </row>
@@ -980,14 +980,14 @@
         <v>324019.42</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>16084</v>
+        <v>18953.88</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>16740.97</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>LT_FY26_Results.pdf p.11 (balance sheet), p.2 (Consolidated PAT, incl. one-time labour-code exceptional provision), p.13 (cash flow)</t>
+          <t>LT_FY26_Results.pdf p.11 (balance sheet), p.10 line 9 "Net profit after tax including share in profit/(loss) of joint ventures/associates" = 18953.88 total group profit (owners 16083.99 + non-controlling interests 2869.89) -- total used, not the attributable slice, to stay consistent with group CFO and group total assets; includes the one-time labour-code exceptional provision, p.13 (cash flow)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>NCC_AR_FY26.pdf p.249-250 (balance sheet) p.251 (P&amp;L) p.254-255 (cash flow)</t>
+          <t>NCC_AR_FY26.pdf p.249-250 (balance sheet) p.251 (P&amp;L "Profit for the year" 723.96 = total group profit, of which non-controlling interests 48.64) p.254-255 (cash flow)</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>PSP_AR_FY26.pdf p.212 (balance sheet) p.213 (P&amp;L) p.214 (cash flow), converted Rs Lakh to Rs Crore (/100)</t>
+          <t>PSP_AR_FY26.pdf p.212 (balance sheet) p.213 (P&amp;L: 5559.21 profit before JV share, less JV share of loss 7.63 = 5551.58) p.214 (cash flow); Rs Lakh converted to Rs Crore (/100). Non-controlling interests are nil, so this is total group profit.</t>
         </is>
       </c>
     </row>
